--- a/docs/xlsx/jobs-2026-09-26.xlsx
+++ b/docs/xlsx/jobs-2026-09-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,73 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>International Director</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 100.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d852f77e72ba40dda49e247286bc7cf5-international-director-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>Staff Accountant II</t>
+  </si>
+  <si>
+    <t>College Success Foundation</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 33.03 - 49.54/hour</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8525fb796f1248aba2e0b40ee81f7420-staff-accountant-ii-college-success-foundation-bellevue</t>
+  </si>
+  <si>
+    <t>Youth Programs Manager</t>
+  </si>
+  <si>
+    <t>CITYSPROUTS INC</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/675c18f8cc3845e5966ccac73d89532e-youth-programs-manager-citysprouts-inc-cambridge</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +114,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +140,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +579,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +618,82 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-26.xlsx
+++ b/docs/xlsx/jobs-2026-09-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
   <si>
     <t>Title</t>
   </si>
@@ -40,15 +40,30 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Interim Chief Operations Officer</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 6500.00 - 8000.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1fd8621365b54f5483c2658df402a6f6-interim-chief-operations-officer-los-angeles</t>
+  </si>
+  <si>
     <t>International Director</t>
   </si>
   <si>
     <t>Swift Sports Organisation</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>Contract</t>
   </si>
   <si>
@@ -61,6 +76,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/d852f77e72ba40dda49e247286bc7cf5-international-director-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>Program Officer</t>
+  </si>
+  <si>
+    <t>SPOON</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d541edb8f1104a8eb0792c371951eac9-program-officer-spoon-portland</t>
+  </si>
+  <si>
     <t>Staff Accountant II</t>
   </si>
   <si>
@@ -70,16 +103,28 @@
     <t>Bellevue, Washington</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 33.03 - 49.54/hour</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/8525fb796f1248aba2e0b40ee81f7420-staff-accountant-ii-college-success-foundation-bellevue</t>
+  </si>
+  <si>
+    <t>Volunteer Manager</t>
+  </si>
+  <si>
+    <t>Child Creativity Lab</t>
+  </si>
+  <si>
+    <t>Santa Ana, California</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7be1bc4f1a8e4c088815f461c6702a5f-volunteer-manager-child-creativity-lab-santa-ana</t>
   </si>
   <si>
     <t>Youth Programs Manager</t>
@@ -579,7 +624,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -635,56 +680,125 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="H3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="H4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="B5" t="s">
         <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -693,6 +807,9 @@
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
